--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>975.5599999999999</v>
+        <v>940.4400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>165.44</v>
+        <v>164.51</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>2229000</v>
+        <v>1828000</v>
       </c>
       <c r="J8" t="n">
-        <v>595061.38</v>
+        <v>618346.73</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>290500</v>
+        <v>257500</v>
       </c>
       <c r="J9" t="n">
-        <v>67535.34</v>
+        <v>69993.14999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>76260</v>
+        <v>67100</v>
       </c>
       <c r="J10" t="n">
-        <v>12123.54</v>
+        <v>12620.8</v>
       </c>
     </row>
     <row r="11">
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1745</v>
+        <v>1755</v>
       </c>
       <c r="J11" t="n">
-        <v>214.99</v>
+        <v>222.72</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>940.4400000000001</v>
+        <v>983.12</v>
       </c>
       <c r="J7" t="n">
-        <v>164.51</v>
+        <v>165.4</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1828000</v>
+        <v>1941000</v>
       </c>
       <c r="J8" t="n">
         <v>618346.73</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>257500</v>
+        <v>268000</v>
       </c>
       <c r="J9" t="n">
         <v>69993.14999999999</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>67100</v>
+        <v>69100</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1755</v>
+        <v>1757.82</v>
       </c>
       <c r="J11" t="n">
         <v>222.72</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>983.12</v>
+        <v>904.28</v>
       </c>
       <c r="J7" t="n">
         <v>165.4</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1941000</v>
+        <v>2022000</v>
       </c>
       <c r="J8" t="n">
         <v>618346.73</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>268000</v>
+        <v>273500</v>
       </c>
       <c r="J9" t="n">
         <v>69993.14999999999</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>69100</v>
+        <v>73100</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1757.82</v>
+        <v>1615</v>
       </c>
       <c r="J11" t="n">
-        <v>222.72</v>
+        <v>225.91</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>904.28</v>
+        <v>853.2</v>
       </c>
       <c r="J7" t="n">
         <v>165.4</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>2022000</v>
+        <v>1830000</v>
       </c>
       <c r="J8" t="n">
-        <v>618346.73</v>
+        <v>628590.24</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>273500</v>
+        <v>253500</v>
       </c>
       <c r="J9" t="n">
         <v>69993.14999999999</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>73100</v>
+        <v>62110</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1615</v>
+        <v>1411.08</v>
       </c>
       <c r="J11" t="n">
         <v>225.91</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>853.2</v>
+        <v>848.95</v>
       </c>
       <c r="J7" t="n">
-        <v>165.4</v>
+        <v>165.63</v>
       </c>
     </row>
     <row r="8">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>62110</v>
+        <v>52110</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1411.08</v>
+        <v>1354.82</v>
       </c>
       <c r="J11" t="n">
         <v>225.91</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>848.95</v>
+        <v>970.8200000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>165.63</v>
+        <v>166.43</v>
       </c>
     </row>
     <row r="8">
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1830000</v>
+        <v>1872000</v>
       </c>
       <c r="J8" t="n">
         <v>628590.24</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>253500</v>
+        <v>263500</v>
       </c>
       <c r="J9" t="n">
-        <v>69993.14999999999</v>
+        <v>70989.53</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>52110</v>
+        <v>61060</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1354.82</v>
+        <v>1589.4</v>
       </c>
       <c r="J11" t="n">
-        <v>225.91</v>
+        <v>228.16</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>970.8200000000001</v>
+        <v>959.48</v>
       </c>
       <c r="J7" t="n">
         <v>166.43</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1872000</v>
+        <v>1830000</v>
       </c>
       <c r="J8" t="n">
         <v>628590.24</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>263500</v>
+        <v>260000</v>
       </c>
       <c r="J9" t="n">
         <v>70989.53</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>61060</v>
+        <v>64270</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1589.4</v>
+        <v>1599.27</v>
       </c>
       <c r="J11" t="n">
-        <v>228.16</v>
+        <v>232.12</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>959.48</v>
+        <v>990.21</v>
       </c>
       <c r="J7" t="n">
         <v>166.43</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1830000</v>
+        <v>1947000</v>
       </c>
       <c r="J8" t="n">
-        <v>628590.24</v>
+        <v>624507.25</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>260000</v>
+        <v>273000</v>
       </c>
       <c r="J9" t="n">
         <v>70989.53</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>64270</v>
+        <v>61880</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1599.27</v>
+        <v>1610.33</v>
       </c>
       <c r="J11" t="n">
-        <v>232.12</v>
+        <v>228.83</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>990.21</v>
+        <v>920.95</v>
       </c>
       <c r="J7" t="n">
-        <v>166.43</v>
+        <v>163.98</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1947000</v>
+        <v>1781000</v>
       </c>
       <c r="J8" t="n">
-        <v>624507.25</v>
+        <v>638717.5600000001</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>273000</v>
+        <v>252500</v>
       </c>
       <c r="J9" t="n">
-        <v>70989.53</v>
+        <v>74664.88</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>61880</v>
+        <v>56010</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1610.33</v>
+        <v>1436.56</v>
       </c>
       <c r="J11" t="n">
         <v>228.83</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>920.95</v>
+        <v>900.2</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1781000</v>
+        <v>1819000</v>
       </c>
       <c r="J8" t="n">
         <v>638717.5600000001</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>252500</v>
+        <v>255000</v>
       </c>
       <c r="J9" t="n">
         <v>74664.88</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>56010</v>
+        <v>54550</v>
       </c>
       <c r="J10" t="n">
         <v>12620.8</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1436.56</v>
+        <v>1278.23</v>
       </c>
       <c r="J11" t="n">
-        <v>228.83</v>
+        <v>229.54</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>900.2</v>
+        <v>820.53</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1819000</v>
+        <v>1525000</v>
       </c>
       <c r="J8" t="n">
         <v>638717.5600000001</v>
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>255000</v>
+        <v>218000</v>
       </c>
       <c r="J9" t="n">
         <v>74664.88</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54550</v>
+        <v>44550</v>
       </c>
       <c r="J10" t="n">
-        <v>12620.8</v>
+        <v>12735.58</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1278.23</v>
+        <v>1096.1</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>820.53</v>
+        <v>739</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1525000</v>
+        <v>1410000</v>
       </c>
       <c r="J8" t="n">
-        <v>638717.5600000001</v>
+        <v>627380.75</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>218000</v>
+        <v>214000</v>
       </c>
       <c r="J9" t="n">
         <v>74664.88</v>
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>44550</v>
+        <v>38380</v>
       </c>
       <c r="J10" t="n">
-        <v>12735.58</v>
+        <v>12897.78</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1096.1</v>
+        <v>1015.89</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>739</v>
+        <v>874.66</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1410000</v>
+        <v>1359000</v>
       </c>
       <c r="J8" t="n">
-        <v>627380.75</v>
+        <v>618749</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>214000</v>
+        <v>213500</v>
       </c>
       <c r="J9" t="n">
-        <v>74664.88</v>
+        <v>75154.77</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>38380</v>
+        <v>39500</v>
       </c>
       <c r="J10" t="n">
         <v>12897.78</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1015.89</v>
+        <v>1279.96</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>874.66</v>
+        <v>823.03</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1359000</v>
+        <v>1718000</v>
       </c>
       <c r="J8" t="n">
-        <v>618749</v>
+        <v>623861.92</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>213500</v>
+        <v>259000</v>
       </c>
       <c r="J9" t="n">
-        <v>75154.77</v>
+        <v>73835.64999999999</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>39500</v>
+        <v>46500</v>
       </c>
       <c r="J10" t="n">
-        <v>12897.78</v>
+        <v>13446.72</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1279.96</v>
+        <v>1214.83</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>823.03</v>
+        <v>814.2</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,7 +3842,7 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1718000</v>
+        <v>1521000</v>
       </c>
       <c r="J8" t="n">
         <v>623861.92</v>
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>259000</v>
+        <v>233500</v>
       </c>
       <c r="J9" t="n">
-        <v>73835.64999999999</v>
+        <v>75167.45</v>
       </c>
     </row>
     <row r="10">
@@ -3910,10 +3910,10 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>46500</v>
+        <v>49160</v>
       </c>
       <c r="J10" t="n">
-        <v>13446.72</v>
+        <v>13503.49</v>
       </c>
     </row>
     <row r="11">
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1214.83</v>
+        <v>1257.1</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>814.2</v>
+        <v>892.67</v>
       </c>
       <c r="J7" t="n">
         <v>163.98</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1521000</v>
+        <v>1609000</v>
       </c>
       <c r="J8" t="n">
-        <v>623861.92</v>
+        <v>584466.4</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>233500</v>
+        <v>242000</v>
       </c>
       <c r="J9" t="n">
-        <v>75167.45</v>
+        <v>75743.41</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>49160</v>
+        <v>52090</v>
       </c>
       <c r="J10" t="n">
         <v>13503.49</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1257.1</v>
+        <v>1427.62</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,10 +3808,10 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>892.67</v>
+        <v>893.1900000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>163.98</v>
+        <v>163.77</v>
       </c>
     </row>
     <row r="8">
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1609000</v>
+        <v>1616000</v>
       </c>
       <c r="J8" t="n">
-        <v>584466.4</v>
+        <v>584336.71</v>
       </c>
     </row>
     <row r="9">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>52090</v>
+        <v>54300</v>
       </c>
       <c r="J10" t="n">
         <v>13503.49</v>
@@ -3944,7 +3944,7 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1427.62</v>
+        <v>1350.5</v>
       </c>
       <c r="J11" t="n">
         <v>229.54</v>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>893.1900000000001</v>
+        <v>881.47</v>
       </c>
       <c r="J7" t="n">
         <v>163.77</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1616000</v>
+        <v>1496000</v>
       </c>
       <c r="J8" t="n">
-        <v>584336.71</v>
+        <v>582766.8</v>
       </c>
     </row>
     <row r="9">
@@ -3876,7 +3876,7 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>242000</v>
+        <v>230000</v>
       </c>
       <c r="J9" t="n">
         <v>75743.41</v>
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>54300</v>
+        <v>48740</v>
       </c>
       <c r="J10" t="n">
         <v>13503.49</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1350.5</v>
+        <v>1258.58</v>
       </c>
       <c r="J11" t="n">
-        <v>229.54</v>
+        <v>237.52</v>
       </c>
     </row>
   </sheetData>

--- a/memoria/memoria-resumo.xlsx
+++ b/memoria/memoria-resumo.xlsx
@@ -3808,7 +3808,7 @@
         <v>1120</v>
       </c>
       <c r="I7" t="n">
-        <v>881.47</v>
+        <v>865.73</v>
       </c>
       <c r="J7" t="n">
         <v>163.77</v>
@@ -3842,10 +3842,10 @@
         <v>728</v>
       </c>
       <c r="I8" t="n">
-        <v>1496000</v>
+        <v>1466000</v>
       </c>
       <c r="J8" t="n">
-        <v>582766.8</v>
+        <v>580750.16</v>
       </c>
     </row>
     <row r="9">
@@ -3876,10 +3876,10 @@
         <v>5969</v>
       </c>
       <c r="I9" t="n">
-        <v>230000</v>
+        <v>235000</v>
       </c>
       <c r="J9" t="n">
-        <v>75743.41</v>
+        <v>75198.12</v>
       </c>
     </row>
     <row r="10">
@@ -3910,7 +3910,7 @@
         <v>540</v>
       </c>
       <c r="I10" t="n">
-        <v>48740</v>
+        <v>47730</v>
       </c>
       <c r="J10" t="n">
         <v>13503.49</v>
@@ -3944,10 +3944,10 @@
         <v>145</v>
       </c>
       <c r="I11" t="n">
-        <v>1258.58</v>
+        <v>1215.98</v>
       </c>
       <c r="J11" t="n">
-        <v>237.52</v>
+        <v>237.45</v>
       </c>
     </row>
   </sheetData>
